--- a/excel-files/NAVOTAS/SAN RAFAEL VILL. ELEMENTARY SCHOOL.xlsx
+++ b/excel-files/NAVOTAS/SAN RAFAEL VILL. ELEMENTARY SCHOOL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29602"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29922"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="41" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1438CED9-1CEB-4899-9484-35E6287A0E39}"/>
+  <xr:revisionPtr revIDLastSave="66" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8FE605AB-A8DF-4439-806F-D5AA1EC9BC02}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="92">
   <si>
     <t>Grade Level</t>
   </si>
@@ -82,6 +82,9 @@
     <t>Math</t>
   </si>
   <si>
+    <t>CO</t>
+  </si>
+  <si>
     <t>Science</t>
   </si>
   <si>
@@ -89,9 +92,6 @@
   </si>
   <si>
     <t>Filipino</t>
-  </si>
-  <si>
-    <t>CO</t>
   </si>
   <si>
     <t>Araling Panlipunan</t>
@@ -631,7 +631,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -742,6 +742,15 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -753,18 +762,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3632,15 +3629,13 @@
       <c r="B6" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="1">
-        <v>90</v>
-      </c>
+      <c r="C6" s="1"/>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
       <c r="F6" s="5"/>
       <c r="G6" s="3">
         <f t="shared" si="0"/>
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="H6" s="4">
         <f t="shared" si="1"/>
@@ -3719,17 +3714,25 @@
       <c r="B11" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="5"/>
+      <c r="C11" s="1">
+        <v>101</v>
+      </c>
+      <c r="D11" s="1">
+        <v>126</v>
+      </c>
+      <c r="E11" s="1">
+        <v>2026</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="G11" s="3">
         <f>IF((C11-D11)&lt;0,0,C11-D11)</f>
         <v>0</v>
       </c>
       <c r="H11" s="4">
         <f>IF((D11-C11)&lt;0,0,D11-C11)</f>
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="19.149999999999999">
@@ -3822,7 +3825,7 @@
         <v>3</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
@@ -3892,7 +3895,7 @@
         <v>4</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C21" s="1">
         <v>113</v>
@@ -3914,7 +3917,7 @@
         <v>4</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C22" s="1">
         <v>113</v>
@@ -3926,7 +3929,7 @@
         <v>2024</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G22" s="3">
         <f t="shared" si="4"/>
@@ -3954,7 +3957,7 @@
         <v>2025</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G23" s="3">
         <f t="shared" si="4"/>
@@ -3982,7 +3985,7 @@
         <v>2025</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G24" s="3">
         <f t="shared" si="4"/>
@@ -4010,7 +4013,7 @@
         <v>2024</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G25" s="3">
         <f t="shared" si="4"/>
@@ -4026,7 +4029,7 @@
         <v>4</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C26" s="1">
         <v>113</v>
@@ -4038,7 +4041,7 @@
         <v>2024</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G26" s="3">
         <f t="shared" si="4"/>
@@ -4066,7 +4069,7 @@
         <v>2024</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G27" s="3">
         <f t="shared" si="4"/>
@@ -4109,16 +4112,22 @@
       <c r="C29" s="1">
         <v>113</v>
       </c>
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
-      <c r="F29" s="5"/>
+      <c r="D29" s="1">
+        <v>173</v>
+      </c>
+      <c r="E29" s="1">
+        <v>2026</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="G29" s="3">
         <f t="shared" si="4"/>
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="H29" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="27.75" customHeight="1">
@@ -4136,21 +4145,27 @@
         <v>5</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C31" s="1">
         <v>104</v>
       </c>
-      <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
-      <c r="F31" s="5"/>
+      <c r="D31" s="1">
+        <v>130</v>
+      </c>
+      <c r="E31" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="G31" s="3">
         <f t="shared" ref="G31:G39" si="6">IF((C31-D31)&lt;0,0,C31-D31)</f>
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="H31" s="4">
         <f t="shared" ref="H31:H39" si="7">IF((D31-C31)&lt;0,0,D31-C31)</f>
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="27.75" customHeight="1">
@@ -4158,7 +4173,7 @@
         <v>5</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C32" s="1">
         <v>104</v>
@@ -4236,7 +4251,7 @@
         <v>2025</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G35" s="3">
         <f t="shared" si="6"/>
@@ -4252,21 +4267,27 @@
         <v>5</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C36" s="1">
         <v>104</v>
       </c>
-      <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
-      <c r="F36" s="5"/>
+      <c r="D36" s="1">
+        <v>130</v>
+      </c>
+      <c r="E36" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F36" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="G36" s="3">
         <f t="shared" si="6"/>
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="H36" s="4">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="27.75" customHeight="1">
@@ -4285,7 +4306,9 @@
       <c r="E37" s="1">
         <v>2025</v>
       </c>
-      <c r="F37" s="5"/>
+      <c r="F37" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="G37" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
@@ -4305,16 +4328,22 @@
       <c r="C38" s="1">
         <v>104</v>
       </c>
-      <c r="D38" s="1"/>
-      <c r="E38" s="1"/>
-      <c r="F38" s="5"/>
+      <c r="D38" s="1">
+        <v>130</v>
+      </c>
+      <c r="E38" s="1">
+        <v>2026</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="G38" s="3">
         <f t="shared" si="6"/>
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="H38" s="4">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="27.75" customHeight="1">
@@ -4354,7 +4383,7 @@
         <v>6</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
@@ -4374,7 +4403,7 @@
         <v>6</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C42" s="1"/>
       <c r="D42" s="1"/>
@@ -4454,7 +4483,7 @@
         <v>6</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
@@ -4544,7 +4573,7 @@
         <v>7</v>
       </c>
       <c r="B51" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="10"/>
@@ -4564,7 +4593,7 @@
         <v>7</v>
       </c>
       <c r="B52" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C52" s="10"/>
       <c r="D52" s="10"/>
@@ -4644,7 +4673,7 @@
         <v>7</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C56" s="10"/>
       <c r="D56" s="10"/>
@@ -4734,7 +4763,7 @@
         <v>8</v>
       </c>
       <c r="B61" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="10"/>
@@ -4754,7 +4783,7 @@
         <v>8</v>
       </c>
       <c r="B62" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C62" s="10"/>
       <c r="D62" s="10"/>
@@ -4834,7 +4863,7 @@
         <v>8</v>
       </c>
       <c r="B66" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C66" s="10"/>
       <c r="D66" s="10"/>
@@ -4924,7 +4953,7 @@
         <v>9</v>
       </c>
       <c r="B71" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="10"/>
@@ -4944,7 +4973,7 @@
         <v>9</v>
       </c>
       <c r="B72" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C72" s="10"/>
       <c r="D72" s="10"/>
@@ -5024,7 +5053,7 @@
         <v>9</v>
       </c>
       <c r="B76" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C76" s="10"/>
       <c r="D76" s="10"/>
@@ -5114,7 +5143,7 @@
         <v>10</v>
       </c>
       <c r="B81" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="10"/>
@@ -5134,7 +5163,7 @@
         <v>10</v>
       </c>
       <c r="B82" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C82" s="10"/>
       <c r="D82" s="10"/>
@@ -5214,7 +5243,7 @@
         <v>10</v>
       </c>
       <c r="B86" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C86" s="10"/>
       <c r="D86" s="10"/>
@@ -5461,13 +5490,14 @@
     </row>
   </sheetData>
   <protectedRanges>
-    <protectedRange sqref="C1:E98" name="Textbooks"/>
+    <protectedRange sqref="C1:E10 C12:E98 D11:E11" name="Textbooks"/>
     <protectedRange sqref="F1:F98" name="SOURCE"/>
+    <protectedRange sqref="C11" name="Textbooks_1"/>
   </protectedRanges>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E14:E19 E21:E29 E31:E39 E51:E59 E61:E69 E41:E49 E2:E6 E71:E79 E81:E89 E8:E12 E91:E98" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E91:E98 E81:E89 E71:E79 E61:E69 E51:E59 E41:E49 E31:E39 E21:E29 E14:E19 E8:E12 E2:E6" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F21:F29 F31:F39 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F2:F6 F8:F12 F91:F98" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
       <formula1>"CO,RO,SDO"</formula1>
@@ -5482,7 +5512,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0858F8C8-8AF8-4852-B88C-61047AF726C8}">
-  <dimension ref="A1:AA157"/>
+  <dimension ref="A1:AA127"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -5512,38 +5542,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
-      <c r="D1" s="40" t="s">
+      <c r="D1" s="43" t="s">
         <v>34</v>
       </c>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
-      <c r="J1" s="41" t="s">
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+      <c r="I1" s="43"/>
+      <c r="J1" s="44" t="s">
         <v>35</v>
       </c>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
-      <c r="P1" s="42" t="s">
+      <c r="K1" s="44"/>
+      <c r="L1" s="44"/>
+      <c r="M1" s="44"/>
+      <c r="N1" s="44"/>
+      <c r="O1" s="44"/>
+      <c r="P1" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="Q1" s="42"/>
-      <c r="R1" s="42"/>
-      <c r="S1" s="42"/>
-      <c r="T1" s="42"/>
-      <c r="U1" s="42"/>
-      <c r="V1" s="43" t="s">
+      <c r="Q1" s="45"/>
+      <c r="R1" s="45"/>
+      <c r="S1" s="45"/>
+      <c r="T1" s="45"/>
+      <c r="U1" s="45"/>
+      <c r="V1" s="46" t="s">
         <v>37</v>
       </c>
-      <c r="W1" s="43"/>
-      <c r="X1" s="43"/>
-      <c r="Y1" s="43"/>
-      <c r="Z1" s="43"/>
-      <c r="AA1" s="43"/>
+      <c r="W1" s="46"/>
+      <c r="X1" s="46"/>
+      <c r="Y1" s="46"/>
+      <c r="Z1" s="46"/>
+      <c r="AA1" s="46"/>
     </row>
     <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
       <c r="A2" s="15" t="s">
@@ -5582,10 +5612,10 @@
       <c r="L2" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="M2" s="46" t="s">
+      <c r="M2" s="41" t="s">
         <v>47</v>
       </c>
-      <c r="N2" s="46" t="s">
+      <c r="N2" s="41" t="s">
         <v>48</v>
       </c>
       <c r="O2" s="22" t="s">
@@ -5618,10 +5648,10 @@
       <c r="X2" s="27" t="s">
         <v>58</v>
       </c>
-      <c r="Y2" s="47" t="s">
+      <c r="Y2" s="42" t="s">
         <v>59</v>
       </c>
-      <c r="Z2" s="47" t="s">
+      <c r="Z2" s="42" t="s">
         <v>60</v>
       </c>
       <c r="AA2" s="26" t="s">
@@ -6057,7 +6087,7 @@
         <v>1</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="5">
@@ -6126,7 +6156,7 @@
         <v>1</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="5">
@@ -6654,7 +6684,7 @@
         <v>2</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C19" s="1">
         <v>101</v>
@@ -6737,7 +6767,7 @@
         <v>2</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C20" s="1">
         <v>101</v>
@@ -7118,7 +7148,7 @@
         <v>3</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C26" s="1">
         <v>121</v>
@@ -7343,7 +7373,7 @@
         <v>3</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C29" s="1">
         <v>121</v>
@@ -7420,7 +7450,7 @@
         <v>3</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C30" s="1">
         <v>121</v>
@@ -7588,7 +7618,7 @@
         <v>4</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C33" s="1"/>
       <c r="D33" s="5">
@@ -7657,7 +7687,7 @@
         <v>4</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C34" s="1"/>
       <c r="D34" s="5">
@@ -7933,7 +7963,7 @@
         <v>4</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="5">
@@ -8225,7 +8255,7 @@
         <v>5</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C43" s="1">
         <v>104</v>
@@ -8308,7 +8338,7 @@
         <v>5</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C44" s="1">
         <v>104</v>
@@ -8622,7 +8652,7 @@
         <v>5</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C48" s="1">
         <v>104</v>
@@ -8944,7 +8974,7 @@
         <v>6</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C53" s="1"/>
       <c r="D53" s="5">
@@ -9013,7 +9043,7 @@
         <v>6</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C54" s="1"/>
       <c r="D54" s="5">
@@ -9289,7 +9319,7 @@
         <v>6</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C58" s="1"/>
       <c r="D58" s="5">
@@ -9579,7 +9609,7 @@
         <v>7</v>
       </c>
       <c r="B63" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="12">
@@ -9648,7 +9678,7 @@
         <v>7</v>
       </c>
       <c r="B64" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C64" s="10"/>
       <c r="D64" s="12">
@@ -9924,7 +9954,7 @@
         <v>7</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C68" s="10"/>
       <c r="D68" s="12">
@@ -10214,7 +10244,7 @@
         <v>8</v>
       </c>
       <c r="B73" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="12">
@@ -10283,7 +10313,7 @@
         <v>8</v>
       </c>
       <c r="B74" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C74" s="10"/>
       <c r="D74" s="12">
@@ -10559,7 +10589,7 @@
         <v>8</v>
       </c>
       <c r="B78" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C78" s="10"/>
       <c r="D78" s="12">
@@ -10849,7 +10879,7 @@
         <v>9</v>
       </c>
       <c r="B83" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="12">
@@ -10918,7 +10948,7 @@
         <v>9</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C84" s="10"/>
       <c r="D84" s="12">
@@ -11194,7 +11224,7 @@
         <v>9</v>
       </c>
       <c r="B88" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C88" s="10"/>
       <c r="D88" s="12">
@@ -11484,7 +11514,7 @@
         <v>10</v>
       </c>
       <c r="B93" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="12">
@@ -11553,7 +11583,7 @@
         <v>10</v>
       </c>
       <c r="B94" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C94" s="10"/>
       <c r="D94" s="12">
@@ -11829,7 +11859,7 @@
         <v>10</v>
       </c>
       <c r="B98" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C98" s="10"/>
       <c r="D98" s="12">
@@ -13664,186 +13694,6 @@
       <c r="AA127" s="5">
         <f t="shared" si="21"/>
         <v>0</v>
-      </c>
-    </row>
-    <row r="128" spans="1:27">
-      <c r="J128" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="129" spans="10:10">
-      <c r="J129" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="130" spans="10:10">
-      <c r="J130" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="131" spans="10:10">
-      <c r="J131" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="132" spans="10:10">
-      <c r="J132" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="133" spans="10:10">
-      <c r="J133" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="134" spans="10:10">
-      <c r="J134" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="135" spans="10:10">
-      <c r="J135" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="136" spans="10:10">
-      <c r="J136" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="137" spans="10:10">
-      <c r="J137" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="138" spans="10:10">
-      <c r="J138" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="139" spans="10:10">
-      <c r="J139" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="140" spans="10:10">
-      <c r="J140" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="141" spans="10:10">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="10:10">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="10:10">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="10:10">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
       </c>
     </row>
   </sheetData>
@@ -13863,8 +13713,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S112:S127 M112:M127 Y112:Y127 G112:G127" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X23:X31 X33:X41 X43:X51 X63:X71 X73:X81 X53:X61 L112:L127 X83:X91 X93:X101 X14:X21 X5:X12 L23:L31 L33:L41 L43:L51 L63:L71 L73:L81 L53:L61 R112:R127 L83:L91 L93:L101 L14:L21 L5:L12 R23:R31 R33:R41 R43:R51 R63:R71 R73:R81 R53:R61 F112:F127 R83:R91 R93:R101 R14:R21 R5:R12 F23:F31 F33:F41 F43:F51 F63:F71 F73:F81 F53:F61 F5:F12 F83:F91 F93:F101 F14:F21 F103:F110 R103:R110 L103:L110 X103:X110 X112:X127" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F112:F127 F103:F110 F93:F101 F83:F91 F73:F81 F63:F71 F53:F61 F43:F51 F33:F41 F23:F31 F14:F21 F5:F12 L112:L127 L103:L110 L93:L101 L83:L91 L73:L81 L63:L71 L53:L61 L43:L51 L33:L41 L23:L31 L14:L21 L5:L12 R112:R127 R103:R110 R93:R101 R83:R91 R73:R81 R63:R71 R53:R61 R43:R51 R33:R41 R23:R31 R14:R21 R5:R12 X112:X127 X103:X110 X93:X101 X83:X91 X73:X81 X63:X71 X53:X61 X43:X51 X33:X41 X23:X31 X14:X21 X5:X12" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M110 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 G14:G21 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
@@ -13882,7 +13732,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F176E3C0-9A94-45E4-9AFD-70DF8ABE5E5A}">
-  <dimension ref="A1:AB171"/>
+  <dimension ref="A1:AB141"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -13912,38 +13762,38 @@
   <sheetData>
     <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
       <c r="B1" s="35"/>
-      <c r="D1" s="40" t="s">
+      <c r="D1" s="43" t="s">
         <v>34</v>
       </c>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
-      <c r="J1" s="41" t="s">
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+      <c r="I1" s="43"/>
+      <c r="J1" s="44" t="s">
         <v>35</v>
       </c>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
-      <c r="P1" s="42" t="s">
+      <c r="K1" s="44"/>
+      <c r="L1" s="44"/>
+      <c r="M1" s="44"/>
+      <c r="N1" s="44"/>
+      <c r="O1" s="44"/>
+      <c r="P1" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="Q1" s="42"/>
-      <c r="R1" s="42"/>
-      <c r="S1" s="42"/>
-      <c r="T1" s="42"/>
-      <c r="U1" s="42"/>
-      <c r="V1" s="43" t="s">
+      <c r="Q1" s="45"/>
+      <c r="R1" s="45"/>
+      <c r="S1" s="45"/>
+      <c r="T1" s="45"/>
+      <c r="U1" s="45"/>
+      <c r="V1" s="46" t="s">
         <v>37</v>
       </c>
-      <c r="W1" s="43"/>
-      <c r="X1" s="43"/>
-      <c r="Y1" s="43"/>
-      <c r="Z1" s="43"/>
-      <c r="AA1" s="43"/>
+      <c r="W1" s="46"/>
+      <c r="X1" s="46"/>
+      <c r="Y1" s="46"/>
+      <c r="Z1" s="46"/>
+      <c r="AA1" s="46"/>
     </row>
     <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
       <c r="A2" s="15" t="s">
@@ -13982,10 +13832,10 @@
       <c r="L2" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="M2" s="46" t="s">
+      <c r="M2" s="41" t="s">
         <v>73</v>
       </c>
-      <c r="N2" s="46" t="s">
+      <c r="N2" s="41" t="s">
         <v>74</v>
       </c>
       <c r="O2" s="22" t="s">
@@ -14018,10 +13868,10 @@
       <c r="X2" s="27" t="s">
         <v>84</v>
       </c>
-      <c r="Y2" s="47" t="s">
+      <c r="Y2" s="42" t="s">
         <v>85</v>
       </c>
-      <c r="Z2" s="47" t="s">
+      <c r="Z2" s="42" t="s">
         <v>86</v>
       </c>
       <c r="AA2" s="26" t="s">
@@ -14098,7 +13948,7 @@
       </c>
     </row>
     <row r="4" spans="1:27" ht="19.5">
-      <c r="A4" s="44"/>
+      <c r="A4" s="40"/>
       <c r="B4" s="33"/>
       <c r="C4" s="34"/>
       <c r="D4" s="34">
@@ -14108,11 +13958,11 @@
       <c r="E4" s="34"/>
       <c r="F4" s="32"/>
       <c r="G4" s="34"/>
-      <c r="H4" s="45">
+      <c r="H4" s="34">
         <f>IF((D4-E4)&lt;0,0,(D4-E4))</f>
         <v>0</v>
       </c>
-      <c r="I4" s="45">
+      <c r="I4" s="34">
         <f>IF((E4-D4)&lt;0,0,(E4-D4))</f>
         <v>0</v>
       </c>
@@ -14443,7 +14293,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="5">
@@ -14512,7 +14362,7 @@
         <v>1</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="5">
@@ -15018,7 +14868,7 @@
         <v>2</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C18" s="1">
         <v>101</v>
@@ -15101,7 +14951,7 @@
         <v>2</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C19" s="1">
         <v>101</v>
@@ -15469,7 +15319,7 @@
         <v>3</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C25" s="1">
         <v>121</v>
@@ -15694,7 +15544,7 @@
         <v>3</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C28" s="1">
         <v>121</v>
@@ -15777,7 +15627,7 @@
         <v>3</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C29" s="1">
         <v>121</v>
@@ -15932,7 +15782,7 @@
         <v>4</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C32" s="1"/>
       <c r="D32" s="5">
@@ -16001,7 +15851,7 @@
         <v>4</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C33" s="1"/>
       <c r="D33" s="5">
@@ -16277,7 +16127,7 @@
         <v>4</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="5">
@@ -16692,7 +16542,7 @@
         <v>5</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C44" s="1"/>
       <c r="D44" s="5">
@@ -16761,7 +16611,7 @@
         <v>5</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C45" s="1"/>
       <c r="D45" s="5">
@@ -17037,7 +16887,7 @@
         <v>5</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C49" s="1"/>
       <c r="D49" s="5">
@@ -17452,7 +17302,7 @@
         <v>6</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C56" s="1">
         <v>104</v>
@@ -17547,7 +17397,7 @@
         <v>6</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C57" s="1">
         <v>104</v>
@@ -17903,7 +17753,7 @@
         <v>6</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C61" s="1">
         <v>104</v>
@@ -18384,7 +18234,7 @@
         <v>7</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C68" s="10"/>
       <c r="D68" s="12">
@@ -18453,7 +18303,7 @@
         <v>7</v>
       </c>
       <c r="B69" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="12">
@@ -18729,7 +18579,7 @@
         <v>7</v>
       </c>
       <c r="B73" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="12">
@@ -19144,7 +18994,7 @@
         <v>8</v>
       </c>
       <c r="B80" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C80" s="10"/>
       <c r="D80" s="12">
@@ -19213,7 +19063,7 @@
         <v>8</v>
       </c>
       <c r="B81" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="12">
@@ -19489,7 +19339,7 @@
         <v>8</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="12">
@@ -19904,7 +19754,7 @@
         <v>9</v>
       </c>
       <c r="B92" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C92" s="10"/>
       <c r="D92" s="12">
@@ -19973,7 +19823,7 @@
         <v>9</v>
       </c>
       <c r="B93" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="12">
@@ -20249,7 +20099,7 @@
         <v>9</v>
       </c>
       <c r="B97" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="12">
@@ -20664,7 +20514,7 @@
         <v>10</v>
       </c>
       <c r="B104" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C104" s="10"/>
       <c r="D104" s="12">
@@ -20733,7 +20583,7 @@
         <v>10</v>
       </c>
       <c r="B105" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="12">
@@ -21009,7 +20859,7 @@
         <v>10</v>
       </c>
       <c r="B109" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="12">
@@ -22482,186 +22332,6 @@
       <c r="AA141" s="7"/>
       <c r="AB141" s="7"/>
     </row>
-    <row r="142" spans="1:28">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="1:28">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="1:28">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="158" spans="10:10">
-      <c r="J158" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="159" spans="10:10">
-      <c r="J159" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="160" spans="10:10">
-      <c r="J160" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="161" spans="10:10">
-      <c r="J161" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="162" spans="10:10">
-      <c r="J162" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="163" spans="10:10">
-      <c r="J163" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="164" spans="10:10">
-      <c r="J164" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="165" spans="10:10">
-      <c r="J165" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="166" spans="10:10">
-      <c r="J166" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="167" spans="10:10">
-      <c r="J167" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="168" spans="10:10">
-      <c r="J168" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="169" spans="10:10">
-      <c r="J169" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="170" spans="10:10">
-      <c r="J170" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="171" spans="10:10">
-      <c r="J171" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C11 C13:C20 C22:C30 C32:C42 C44:C54 C56:C66 C68:C78 C80:C90 C116:C123 C104:C114 C92:C102" name="Textbooks"/>
@@ -22679,8 +22349,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S116:S123 Y116:Y123 G116:G123 Y3:Y11 S3:S11 M3:M11 G3:G11 G13:G20 Y13:Y20 S13:S20 M13:M20 M22:M30 G22:G30 Y22:Y30 S22:S30 S32:S42 M32:M42 G32:G42 Y32:Y42 Y44:Y54 S44:S54 M44:M54 G44:G54 G56:G66 Y56:Y66 S56:S66 M56:M66 M68:M78 G68:G78 Y68:Y78 S68:S78 S80:S90 M80:M90 G80:G90 Y80:Y90 Y92:Y102 S92:S102 M92:M102 G92:G102 G104:G114 Y104:Y114 S104:S114 M104:M114 M116:M123" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X22:X30 X32:X42 X44:X54 X68:X78 X80:X90 X56:X66 X92:X102 X104:X114 X13:X20 X3:X11 L22:L30 L32:L42 L44:L54 L68:L78 L80:L90 L56:L66 L92:L102 L104:L114 L13:L20 L3:L11 R22:R30 R32:R42 R44:R54 R68:R78 R80:R90 R56:R66 R92:R102 R104:R114 R13:R20 R3:R11 F22:F30 F32:F42 F44:F54 F68:F78 F80:F90 F56:F66 F3:F11 F92:F102 X116:X123 F13:F20 F116:F123 R116:R123 L116:L123 F104:F114" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F116:F123 F104:F114 F92:F102 F80:F90 F68:F78 F56:F66 F44:F54 F32:F42 F22:F30 F13:F20 F3:F11 L116:L123 L104:L114 L92:L102 L80:L90 L68:L78 L56:L66 L44:L54 L32:L42 L22:L30 L13:L20 L3:L11 R116:R123 R104:R114 R92:R102 R80:R90 R68:R78 R56:R66 R44:R54 R32:R42 R22:R30 R13:R20 R3:R11 X116:X123 X104:X114 X92:X102 X80:X90 X68:X78 X56:X66 X44:X54 X32:X42 X22:X30 X13:X20 X3:X11" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
